--- a/classifica_competenze.xlsx
+++ b/classifica_competenze.xlsx
@@ -450,7 +450,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Dir Milano 13</t>
+          <t>Gallino federico</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -471,7 +471,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Dir Milano 12</t>
+          <t>Mura Michele</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -492,7 +492,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Dir Milano 19</t>
+          <t>Vergani Giorgio</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -513,7 +513,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Dir Milano 21</t>
+          <t>Vacca Paolo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -534,7 +534,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dir Milano 6</t>
+          <t>Gerevini Mara Bianca</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dir Milano 1</t>
+          <t>Batavia Marco Filippo</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -576,7 +576,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Dir Milano 5</t>
+          <t>Campestri Ilaria</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -597,7 +597,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Dir Milano 8</t>
+          <t>Riva Mauro</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -618,7 +618,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Dir Milano 4</t>
+          <t>Zilio Stefano</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -639,7 +639,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Dir Milano 22</t>
+          <t>Gigli Jabril</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -660,7 +660,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Dir Milano 18</t>
+          <t xml:space="preserve">Battilana Paolo </t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -681,7 +681,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Dir Milano 17</t>
+          <t>Mio Bertolo Johnny</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Dir Milano 9</t>
+          <t>Giorgi Stefano</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -723,7 +723,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Dir Milano 2</t>
+          <t>Moraja Marco</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -744,7 +744,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Dir Milano 24</t>
+          <t>Cadoppi Andrea</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -765,7 +765,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dir Milano 10</t>
+          <t>Foglia Emanuela</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -786,7 +786,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Dir Milano 25</t>
+          <t>Valcamonica Marco</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -807,7 +807,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Dir Milano 14</t>
+          <t>Rondena Segio</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -828,7 +828,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Dir Milano 3</t>
+          <t>Gallina Paolo</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -849,7 +849,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Dir Milano 15</t>
+          <t>Zucchi Imerio</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -870,7 +870,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Dir Milano 11</t>
+          <t>Alacqua Stefano</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,7 +891,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Dir Milano 20</t>
+          <t>Maccalini Enrico</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Dir Milano 16</t>
+          <t>Nicolosi Dario</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -933,7 +933,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Dir Milano 23</t>
+          <t>Tradani Susanna</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -954,7 +954,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Dir Milano 7</t>
+          <t>Fumagalli Luca</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1016,7 +1016,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Pro Milano 11</t>
+          <t>Milanta Mariapaola</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1037,7 +1037,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pro Milano 4</t>
+          <t>Arco Carmelo</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1058,7 +1058,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pro Milano 7</t>
+          <t>Colombo A lessandra</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1079,7 +1079,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Pro Milano 1</t>
+          <t>Muca Adrian</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pro Milano 8</t>
+          <t>Fernicola Alessandra</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1121,7 +1121,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pro Milano 3</t>
+          <t>Fumagalli Alessandro</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1142,7 +1142,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pro Milano 12</t>
+          <t>Calderoni Gabriele Maria</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1163,7 +1163,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Pro Milano 9</t>
+          <t>Toia Luca Luigi</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1184,7 +1184,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Pro Milano 5</t>
+          <t>Macchi Giorgio</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1205,7 +1205,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Pro Milano 16</t>
+          <t>Cercaci Alessandra</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1226,7 +1226,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pro Milano 13</t>
+          <t>Ceriani Massimo</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1247,7 +1247,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Pro Milano 2</t>
+          <t>Farina Simona</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1268,7 +1268,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Pro Milano 6</t>
+          <t>Premoli Gianluca</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1289,7 +1289,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Pro Milano 10</t>
+          <t>Campanello Marco</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1310,7 +1310,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Pro Milano 17</t>
+          <t>Roberto Rocca</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1331,7 +1331,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pro Milano 14</t>
+          <t>Valieri Andrea</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1352,7 +1352,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pro Milano 15</t>
+          <t>Mauri Luca</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1381,7 +1381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1414,7 +1414,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Pro Avezzano 4</t>
+          <t>Di Sabatino Bruno</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1423,19 +1423,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3.083333333333333</v>
+        <v>2.916666666666667</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>2.85625</v>
+        <v>2.875</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pro Avezzano 8</t>
+          <t>Francesconi Luigia</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1444,19 +1444,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3.041666666666667</v>
+        <v>2.916666666666667</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>2.85625</v>
+        <v>2.875</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pro Avezzano 13</t>
+          <t>Tartaglia Vincenzo</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1465,19 +1465,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3.041666666666667</v>
+        <v>2.916666666666667</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>2.85625</v>
+        <v>2.875</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Dir Avezzano 1</t>
+          <t>Santella Gianni</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1489,16 +1489,16 @@
         <v>2.916666666666667</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>2.85625</v>
+        <v>2.875</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dir Avezzano 7</t>
+          <t>Santangelo Maurizio</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1507,19 +1507,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2.916666666666667</v>
+        <v>2.875</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>2.85625</v>
+        <v>2.875</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pro Avezzano 11</t>
+          <t xml:space="preserve">Diego Gi Giampietro </t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1528,19 +1528,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2.916666666666667</v>
+        <v>2.791666666666667</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>2.85625</v>
+        <v>2.875</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Dir Avezzano 3</t>
+          <t>Properzi Massimiliano</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1549,286 +1549,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.916666666666667</v>
+        <v>2.791666666666667</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>2.85625</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Dir Avezzano 6</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Dirigente Avezzano</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>2.916666666666667</v>
-      </c>
-      <c r="D9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2.85625</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Pro Avezzano 9</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Dirigente Avezzano</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
         <v>2.875</v>
-      </c>
-      <c r="D10" t="n">
-        <v>9</v>
-      </c>
-      <c r="E10" t="n">
-        <v>2.85625</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Dir Avezzano 5</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Dirigente Avezzano</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>2.875</v>
-      </c>
-      <c r="D11" t="n">
-        <v>9</v>
-      </c>
-      <c r="E11" t="n">
-        <v>2.85625</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Pro Avezzano 2</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Dirigente Avezzano</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>2.875</v>
-      </c>
-      <c r="D12" t="n">
-        <v>9</v>
-      </c>
-      <c r="E12" t="n">
-        <v>2.85625</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Pro Avezzano 14</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Dirigente Avezzano</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>2.833333333333333</v>
-      </c>
-      <c r="D13" t="n">
-        <v>12</v>
-      </c>
-      <c r="E13" t="n">
-        <v>2.85625</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Dir Avezzano 4</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Dirigente Avezzano</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>2.791666666666667</v>
-      </c>
-      <c r="D14" t="n">
-        <v>13</v>
-      </c>
-      <c r="E14" t="n">
-        <v>2.85625</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Dir Avezzano 2</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Dirigente Avezzano</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>2.791666666666667</v>
-      </c>
-      <c r="D15" t="n">
-        <v>13</v>
-      </c>
-      <c r="E15" t="n">
-        <v>2.85625</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Pro Avezzano 3</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Dirigente Avezzano</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="D16" t="n">
-        <v>15</v>
-      </c>
-      <c r="E16" t="n">
-        <v>2.85625</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Pro Avezzano 5</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Dirigente Avezzano</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="D17" t="n">
-        <v>15</v>
-      </c>
-      <c r="E17" t="n">
-        <v>2.85625</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Pro Avezzano 6</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Dirigente Avezzano</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="D18" t="n">
-        <v>15</v>
-      </c>
-      <c r="E18" t="n">
-        <v>2.85625</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Pro Avezzano 12</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Dirigente Avezzano</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="D19" t="n">
-        <v>15</v>
-      </c>
-      <c r="E19" t="n">
-        <v>2.85625</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Pro Avezzano 10</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Dirigente Avezzano</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>2.666666666666667</v>
-      </c>
-      <c r="D20" t="n">
-        <v>19</v>
-      </c>
-      <c r="E20" t="n">
-        <v>2.85625</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Pro Avezzano 7</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Dirigente Avezzano</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>2.666666666666667</v>
-      </c>
-      <c r="D21" t="n">
-        <v>19</v>
-      </c>
-      <c r="E21" t="n">
-        <v>2.85625</v>
       </c>
     </row>
   </sheetData>
@@ -1842,7 +1569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1875,7 +1602,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Pro Avezzano 1</t>
+          <t xml:space="preserve">Di Giacomo Lorenzo </t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1884,13 +1611,286 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2.958333333333333</v>
+        <v>3.083333333333333</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
+        <v>2.854166666666667</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ghidelli Serge</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Professional Avezzano</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>3.041666666666667</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2.854166666666667</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Zaccardelli Giuseppe</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Professional Avezzano</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3.041666666666667</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2.854166666666667</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bianchi Liberato </t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Professional Avezzano</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
         <v>2.958333333333333</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2.854166666666667</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Piccirilli Gianluca</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Professional Avezzano</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2.916666666666667</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2.854166666666667</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Castrigano Luca </t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Professional Avezzano</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2.854166666666667</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Margutti Pasquale</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Professional Avezzano</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2.854166666666667</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Lamura Sabrina</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Professional Avezzano</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2.833333333333333</v>
+      </c>
+      <c r="D9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.854166666666667</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">De Amicis Alvaro </t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Professional Avezzano</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="D10" t="n">
+        <v>9</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.854166666666667</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Di Paolo Massimo</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Professional Avezzano</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="D11" t="n">
+        <v>9</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.854166666666667</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Volpa Alessandra </t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Professional Avezzano</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="D12" t="n">
+        <v>9</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2.854166666666667</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Tellone Giuliano</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Professional Avezzano</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="D13" t="n">
+        <v>9</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.854166666666667</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Palma Luca</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Professional Avezzano</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="D14" t="n">
+        <v>13</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.854166666666667</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Amabrini Fabio</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Professional Avezzano</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="D15" t="n">
+        <v>13</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.854166666666667</v>
       </c>
     </row>
   </sheetData>
@@ -1937,7 +1937,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Pro Milano 11</t>
+          <t>Milanta Mariapaola</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1958,7 +1958,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Dir Milano 13</t>
+          <t>Gallino federico</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1979,7 +1979,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Dir Milano 12</t>
+          <t>Mura Michele</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2000,7 +2000,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Dir Milano 19</t>
+          <t>Vergani Giorgio</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2021,7 +2021,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dir Milano 21</t>
+          <t>Vacca Paolo</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2042,7 +2042,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dir Milano 6</t>
+          <t>Gerevini Mara Bianca</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2063,7 +2063,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pro Milano 4</t>
+          <t>Arco Carmelo</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2084,7 +2084,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Pro Milano 7</t>
+          <t>Colombo A lessandra</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2105,12 +2105,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Pro Avezzano 4</t>
+          <t xml:space="preserve">Di Giacomo Lorenzo </t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Dirigente Avezzano</t>
+          <t>Professional Avezzano</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -2120,13 +2120,13 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>2.85625</v>
+        <v>2.854166666666667</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Dir Milano 1</t>
+          <t>Batavia Marco Filippo</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2147,12 +2147,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pro Avezzano 13</t>
+          <t>Zaccardelli Giuseppe</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Dirigente Avezzano</t>
+          <t>Professional Avezzano</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -2162,18 +2162,18 @@
         <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>2.85625</v>
+        <v>2.854166666666667</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Pro Avezzano 8</t>
+          <t>Ghidelli Serge</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dirigente Avezzano</t>
+          <t>Professional Avezzano</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2183,13 +2183,13 @@
         <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>2.85625</v>
+        <v>2.854166666666667</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Dir Milano 8</t>
+          <t>Riva Mauro</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2210,7 +2210,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Dir Milano 5</t>
+          <t>Campestri Ilaria</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2231,7 +2231,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Dir Milano 9</t>
+          <t>Giorgi Stefano</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2252,7 +2252,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dir Milano 18</t>
+          <t xml:space="preserve">Battilana Paolo </t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2273,7 +2273,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Dir Milano 4</t>
+          <t>Zilio Stefano</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2294,7 +2294,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Dir Milano 17</t>
+          <t>Mio Bertolo Johnny</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2315,7 +2315,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Dir Milano 22</t>
+          <t>Gigli Jabril</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2336,7 +2336,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Pro Milano 1</t>
+          <t>Muca Adrian</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Pro Milano 3</t>
+          <t>Fumagalli Alessandro</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2378,7 +2378,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Dir Milano 24</t>
+          <t>Cadoppi Andrea</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2399,7 +2399,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Dir Milano 2</t>
+          <t>Moraja Marco</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2420,7 +2420,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Pro Avezzano 1</t>
+          <t xml:space="preserve">Bianchi Liberato </t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2432,16 +2432,16 @@
         <v>2.958333333333333</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E25" t="n">
-        <v>2.958333333333333</v>
+        <v>2.854166666666667</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Pro Milano 8</t>
+          <t>Fernicola Alessandra</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2462,7 +2462,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Pro Milano 12</t>
+          <t>Calderoni Gabriele Maria</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2483,7 +2483,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Dir Milano 25</t>
+          <t>Valcamonica Marco</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2504,7 +2504,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Dir Milano 10</t>
+          <t>Foglia Emanuela</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2525,7 +2525,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Dir Milano 14</t>
+          <t>Rondena Segio</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2546,7 +2546,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Dir Avezzano 6</t>
+          <t>Santella Gianni</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2558,16 +2558,16 @@
         <v>2.916666666666667</v>
       </c>
       <c r="D31" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>2.85625</v>
+        <v>2.875</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Dir Avezzano 3</t>
+          <t>Francesconi Luigia</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2579,16 +2579,16 @@
         <v>2.916666666666667</v>
       </c>
       <c r="D32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.85625</v>
+        <v>2.875</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Dir Avezzano 1</t>
+          <t>Di Sabatino Bruno</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2600,16 +2600,16 @@
         <v>2.916666666666667</v>
       </c>
       <c r="D33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>2.85625</v>
+        <v>2.875</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Dir Avezzano 7</t>
+          <t>Tartaglia Vincenzo</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2621,79 +2621,79 @@
         <v>2.916666666666667</v>
       </c>
       <c r="D34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>2.85625</v>
+        <v>2.875</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Pro Avezzano 11</t>
+          <t>Piccirilli Gianluca</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Dirigente Avezzano</t>
+          <t>Professional Avezzano</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>2.916666666666667</v>
       </c>
       <c r="D35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E35" t="n">
-        <v>2.85625</v>
+        <v>2.854166666666667</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Pro Avezzano 2</t>
+          <t xml:space="preserve">Castrigano Luca </t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Dirigente Avezzano</t>
+          <t>Professional Avezzano</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>2.875</v>
       </c>
       <c r="D36" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E36" t="n">
-        <v>2.85625</v>
+        <v>2.854166666666667</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Pro Avezzano 9</t>
+          <t>Margutti Pasquale</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Dirigente Avezzano</t>
+          <t>Professional Avezzano</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>2.875</v>
       </c>
       <c r="D37" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E37" t="n">
-        <v>2.85625</v>
+        <v>2.854166666666667</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Pro Milano 16</t>
+          <t>Cercaci Alessandra</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2714,7 +2714,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Pro Milano 9</t>
+          <t>Toia Luca Luigi</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2735,7 +2735,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Dir Avezzano 5</t>
+          <t>Santangelo Maurizio</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2747,16 +2747,16 @@
         <v>2.875</v>
       </c>
       <c r="D40" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E40" t="n">
-        <v>2.85625</v>
+        <v>2.875</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Pro Milano 5</t>
+          <t>Macchi Giorgio</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2777,7 +2777,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Dir Milano 11</t>
+          <t>Alacqua Stefano</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2798,7 +2798,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Pro Milano 13</t>
+          <t>Ceriani Massimo</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2819,28 +2819,28 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Pro Avezzano 14</t>
+          <t>Lamura Sabrina</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Dirigente Avezzano</t>
+          <t>Professional Avezzano</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>2.833333333333333</v>
       </c>
       <c r="D44" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E44" t="n">
-        <v>2.85625</v>
+        <v>2.854166666666667</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Dir Milano 15</t>
+          <t>Zucchi Imerio</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2861,7 +2861,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Dir Milano 3</t>
+          <t>Gallina Paolo</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2882,7 +2882,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Dir Milano 16</t>
+          <t>Nicolosi Dario</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2903,7 +2903,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Dir Milano 23</t>
+          <t>Tradani Susanna</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2924,7 +2924,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Dir Avezzano 4</t>
+          <t>Properzi Massimiliano</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2936,16 +2936,16 @@
         <v>2.791666666666667</v>
       </c>
       <c r="D49" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E49" t="n">
-        <v>2.85625</v>
+        <v>2.875</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Dir Avezzano 2</t>
+          <t xml:space="preserve">Diego Gi Giampietro </t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2957,16 +2957,16 @@
         <v>2.791666666666667</v>
       </c>
       <c r="D50" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E50" t="n">
-        <v>2.85625</v>
+        <v>2.875</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Dir Milano 20</t>
+          <t>Maccalini Enrico</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2987,7 +2987,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Pro Milano 2</t>
+          <t>Farina Simona</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3008,28 +3008,28 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Pro Avezzano 6</t>
+          <t xml:space="preserve">Volpa Alessandra </t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Dirigente Avezzano</t>
+          <t>Professional Avezzano</t>
         </is>
       </c>
       <c r="C53" t="n">
         <v>2.75</v>
       </c>
       <c r="D53" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E53" t="n">
-        <v>2.85625</v>
+        <v>2.854166666666667</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Pro Milano 6</t>
+          <t>Premoli Gianluca</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3050,7 +3050,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Pro Milano 10</t>
+          <t>Campanello Marco</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3071,7 +3071,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Pro Milano 17</t>
+          <t>Roberto Rocca</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3092,70 +3092,70 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Pro Avezzano 3</t>
+          <t xml:space="preserve">De Amicis Alvaro </t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Dirigente Avezzano</t>
+          <t>Professional Avezzano</t>
         </is>
       </c>
       <c r="C57" t="n">
         <v>2.75</v>
       </c>
       <c r="D57" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E57" t="n">
-        <v>2.85625</v>
+        <v>2.854166666666667</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Pro Avezzano 12</t>
+          <t>Tellone Giuliano</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Dirigente Avezzano</t>
+          <t>Professional Avezzano</t>
         </is>
       </c>
       <c r="C58" t="n">
         <v>2.75</v>
       </c>
       <c r="D58" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E58" t="n">
-        <v>2.85625</v>
+        <v>2.854166666666667</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Pro Avezzano 5</t>
+          <t>Di Paolo Massimo</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Dirigente Avezzano</t>
+          <t>Professional Avezzano</t>
         </is>
       </c>
       <c r="C59" t="n">
         <v>2.75</v>
       </c>
       <c r="D59" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E59" t="n">
-        <v>2.85625</v>
+        <v>2.854166666666667</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Dir Milano 7</t>
+          <t>Fumagalli Luca</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3176,7 +3176,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Pro Milano 14</t>
+          <t>Valieri Andrea</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3197,49 +3197,49 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Pro Avezzano 10</t>
+          <t>Palma Luca</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Dirigente Avezzano</t>
+          <t>Professional Avezzano</t>
         </is>
       </c>
       <c r="C62" t="n">
         <v>2.666666666666667</v>
       </c>
       <c r="D62" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E62" t="n">
-        <v>2.85625</v>
+        <v>2.854166666666667</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Pro Avezzano 7</t>
+          <t>Amabrini Fabio</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Dirigente Avezzano</t>
+          <t>Professional Avezzano</t>
         </is>
       </c>
       <c r="C63" t="n">
         <v>2.666666666666667</v>
       </c>
       <c r="D63" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E63" t="n">
-        <v>2.85625</v>
+        <v>2.854166666666667</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Pro Milano 15</t>
+          <t>Mauri Luca</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">

--- a/classifica_competenze.xlsx
+++ b/classifica_competenze.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,7 +465,7 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>2.976666666666667</v>
+        <v>2.969487179487179</v>
       </c>
     </row>
     <row r="3">
@@ -486,7 +486,7 @@
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>2.976666666666667</v>
+        <v>2.969487179487179</v>
       </c>
     </row>
     <row r="4">
@@ -507,7 +507,7 @@
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>2.976666666666667</v>
+        <v>2.969487179487179</v>
       </c>
     </row>
     <row r="5">
@@ -528,7 +528,7 @@
         <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>2.976666666666667</v>
+        <v>2.969487179487179</v>
       </c>
     </row>
     <row r="6">
@@ -549,7 +549,7 @@
         <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>2.976666666666667</v>
+        <v>2.969487179487179</v>
       </c>
     </row>
     <row r="7">
@@ -570,13 +570,13 @@
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>2.976666666666667</v>
+        <v>2.969487179487179</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Campestri Ilaria</t>
+          <t>Riva Mauro</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -591,13 +591,13 @@
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>2.976666666666667</v>
+        <v>2.969487179487179</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Riva Mauro</t>
+          <t>Campestri Ilaria</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -612,13 +612,13 @@
         <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>2.976666666666667</v>
+        <v>2.969487179487179</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Zilio Stefano</t>
+          <t>Giorgi Stefano</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -633,13 +633,13 @@
         <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>2.976666666666667</v>
+        <v>2.969487179487179</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Gigli Jabril</t>
+          <t>Zilio Stefano</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -654,13 +654,13 @@
         <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>2.976666666666667</v>
+        <v>2.969487179487179</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Battilana Paolo </t>
+          <t>Mio Bertolo Johnny</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -675,13 +675,13 @@
         <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>2.976666666666667</v>
+        <v>2.969487179487179</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Mio Bertolo Johnny</t>
+          <t>Gigli Jabril</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -696,13 +696,13 @@
         <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>2.976666666666667</v>
+        <v>2.969487179487179</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Giorgi Stefano</t>
+          <t xml:space="preserve">Battilana Paolo </t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -717,7 +717,7 @@
         <v>9</v>
       </c>
       <c r="E14" t="n">
-        <v>2.976666666666667</v>
+        <v>2.969487179487179</v>
       </c>
     </row>
     <row r="15">
@@ -738,7 +738,7 @@
         <v>14</v>
       </c>
       <c r="E15" t="n">
-        <v>2.976666666666667</v>
+        <v>2.969487179487179</v>
       </c>
     </row>
     <row r="16">
@@ -759,13 +759,13 @@
         <v>14</v>
       </c>
       <c r="E16" t="n">
-        <v>2.976666666666667</v>
+        <v>2.969487179487179</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Foglia Emanuela</t>
+          <t>Valcamonica Marco</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -780,13 +780,13 @@
         <v>16</v>
       </c>
       <c r="E17" t="n">
-        <v>2.976666666666667</v>
+        <v>2.969487179487179</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Valcamonica Marco</t>
+          <t>Foglia Emanuela</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -801,7 +801,7 @@
         <v>16</v>
       </c>
       <c r="E18" t="n">
-        <v>2.976666666666667</v>
+        <v>2.969487179487179</v>
       </c>
     </row>
     <row r="19">
@@ -822,13 +822,13 @@
         <v>16</v>
       </c>
       <c r="E19" t="n">
-        <v>2.976666666666667</v>
+        <v>2.969487179487179</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gallina Paolo</t>
+          <t>Alacqua Stefano</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -843,13 +843,13 @@
         <v>19</v>
       </c>
       <c r="E20" t="n">
-        <v>2.976666666666667</v>
+        <v>2.969487179487179</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Zucchi Imerio</t>
+          <t>Gallina Paolo</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -864,13 +864,13 @@
         <v>19</v>
       </c>
       <c r="E21" t="n">
-        <v>2.976666666666667</v>
+        <v>2.969487179487179</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alacqua Stefano</t>
+          <t>Zucchi Imerio</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -885,13 +885,13 @@
         <v>19</v>
       </c>
       <c r="E22" t="n">
-        <v>2.976666666666667</v>
+        <v>2.969487179487179</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Maccalini Enrico</t>
+          <t>Nicolosi Dario</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -906,13 +906,13 @@
         <v>22</v>
       </c>
       <c r="E23" t="n">
-        <v>2.976666666666667</v>
+        <v>2.969487179487179</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Nicolosi Dario</t>
+          <t>Tradani Susanna</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -927,13 +927,13 @@
         <v>22</v>
       </c>
       <c r="E24" t="n">
-        <v>2.976666666666667</v>
+        <v>2.969487179487179</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Tradani Susanna</t>
+          <t>Maccalini Enrico</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -948,13 +948,13 @@
         <v>22</v>
       </c>
       <c r="E25" t="n">
-        <v>2.976666666666667</v>
+        <v>2.969487179487179</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Fumagalli Luca</t>
+          <t>De cesaro Franco</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -963,13 +963,34 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2.708333333333333</v>
+        <v>2.79</v>
       </c>
       <c r="D26" t="n">
         <v>25</v>
       </c>
       <c r="E26" t="n">
-        <v>2.976666666666667</v>
+        <v>2.969487179487179</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Fumagalli Luca</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Dirigente Milano</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>2.708333333333333</v>
+      </c>
+      <c r="D27" t="n">
+        <v>26</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2.969487179487179</v>
       </c>
     </row>
   </sheetData>
@@ -1569,7 +1590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1602,7 +1623,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Di Giacomo Lorenzo </t>
+          <t>Di Francesco Roberto</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1611,19 +1632,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3.083333333333333</v>
+        <v>3.12</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>2.854166666666667</v>
+        <v>2.866770833333333</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ghidelli Serge</t>
+          <t xml:space="preserve">Di Giacomo Lorenzo </t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1632,13 +1653,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3.041666666666667</v>
+        <v>3.083333333333333</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>2.854166666666667</v>
+        <v>2.866770833333333</v>
       </c>
     </row>
     <row r="4">
@@ -1656,16 +1677,16 @@
         <v>3.041666666666667</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>2.854166666666667</v>
+        <v>2.866770833333333</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bianchi Liberato </t>
+          <t>Ghidelli Serge</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1674,19 +1695,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2.958333333333333</v>
+        <v>3.041666666666667</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>2.854166666666667</v>
+        <v>2.866770833333333</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Piccirilli Gianluca</t>
+          <t xml:space="preserve">Bianchi Liberato </t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1695,19 +1716,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2.916666666666667</v>
+        <v>2.958333333333333</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>2.854166666666667</v>
+        <v>2.866770833333333</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Castrigano Luca </t>
+          <t>Piccirilli Gianluca</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1716,13 +1737,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2.875</v>
+        <v>2.916666666666667</v>
       </c>
       <c r="D7" t="n">
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>2.854166666666667</v>
+        <v>2.866770833333333</v>
       </c>
     </row>
     <row r="8">
@@ -1740,16 +1761,16 @@
         <v>2.875</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>2.854166666666667</v>
+        <v>2.866770833333333</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Lamura Sabrina</t>
+          <t xml:space="preserve">Castrigano Luca </t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1758,19 +1779,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2.833333333333333</v>
+        <v>2.875</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>2.854166666666667</v>
+        <v>2.866770833333333</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">De Amicis Alvaro </t>
+          <t>Lamura Sabrina</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1779,19 +1800,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2.75</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="D10" t="n">
         <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>2.854166666666667</v>
+        <v>2.866770833333333</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Di Paolo Massimo</t>
+          <t>Alesii Genuino</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1800,19 +1821,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>2.854166666666667</v>
+        <v>2.866770833333333</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Volpa Alessandra </t>
+          <t>Di Paolo Massimo</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1824,16 +1845,16 @@
         <v>2.75</v>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
-        <v>2.854166666666667</v>
+        <v>2.866770833333333</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Tellone Giuliano</t>
+          <t xml:space="preserve">De Amicis Alvaro </t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1845,16 +1866,16 @@
         <v>2.75</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E13" t="n">
-        <v>2.854166666666667</v>
+        <v>2.866770833333333</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Palma Luca</t>
+          <t>Tellone Giuliano</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1863,34 +1884,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2.666666666666667</v>
+        <v>2.75</v>
       </c>
       <c r="D14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E14" t="n">
-        <v>2.854166666666667</v>
+        <v>2.866770833333333</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t xml:space="preserve">Volpa Alessandra </t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Professional Avezzano</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="D15" t="n">
+        <v>11</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.866770833333333</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>Amabrini Fabio</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Professional Avezzano</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="C16" t="n">
         <v>2.666666666666667</v>
       </c>
-      <c r="D15" t="n">
-        <v>13</v>
-      </c>
-      <c r="E15" t="n">
-        <v>2.854166666666667</v>
+      <c r="D16" t="n">
+        <v>15</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2.866770833333333</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Palma Luca</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Professional Avezzano</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="D17" t="n">
+        <v>15</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2.866770833333333</v>
       </c>
     </row>
   </sheetData>
@@ -1904,7 +1967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1973,7 +2036,7 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>2.976666666666667</v>
+        <v>2.969487179487179</v>
       </c>
     </row>
     <row r="4">
@@ -1994,7 +2057,7 @@
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>2.976666666666667</v>
+        <v>2.969487179487179</v>
       </c>
     </row>
     <row r="5">
@@ -2015,7 +2078,7 @@
         <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>2.976666666666667</v>
+        <v>2.969487179487179</v>
       </c>
     </row>
     <row r="6">
@@ -2036,7 +2099,7 @@
         <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>2.976666666666667</v>
+        <v>2.969487179487179</v>
       </c>
     </row>
     <row r="7">
@@ -2057,7 +2120,7 @@
         <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>2.976666666666667</v>
+        <v>2.969487179487179</v>
       </c>
     </row>
     <row r="8">
@@ -2084,64 +2147,64 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Colombo A lessandra</t>
+          <t>Di Francesco Roberto</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Professional Milano</t>
+          <t>Professional Avezzano</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3.083333333333333</v>
+        <v>3.12</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>2.897058823529412</v>
+        <v>2.866770833333333</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Di Giacomo Lorenzo </t>
+          <t>Colombo A lessandra</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Professional Avezzano</t>
+          <t>Professional Milano</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>3.083333333333333</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>2.854166666666667</v>
+        <v>2.897058823529412</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Batavia Marco Filippo</t>
+          <t xml:space="preserve">Di Giacomo Lorenzo </t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dirigente Milano</t>
+          <t>Professional Avezzano</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3.041666666666667</v>
+        <v>3.083333333333333</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>2.976666666666667</v>
+        <v>2.866770833333333</v>
       </c>
     </row>
     <row r="12">
@@ -2159,31 +2222,31 @@
         <v>3.041666666666667</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>2.854166666666667</v>
+        <v>2.866770833333333</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ghidelli Serge</t>
+          <t>Batavia Marco Filippo</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Professional Avezzano</t>
+          <t>Dirigente Milano</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>3.041666666666667</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>2.854166666666667</v>
+        <v>2.969487179487179</v>
       </c>
     </row>
     <row r="14">
@@ -2204,34 +2267,34 @@
         <v>6</v>
       </c>
       <c r="E14" t="n">
-        <v>2.976666666666667</v>
+        <v>2.969487179487179</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Campestri Ilaria</t>
+          <t>Ghidelli Serge</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Dirigente Milano</t>
+          <t>Professional Avezzano</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>3.041666666666667</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>2.976666666666667</v>
+        <v>2.866770833333333</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Giorgi Stefano</t>
+          <t>Campestri Ilaria</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2240,13 +2303,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>3.041666666666667</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>2.976666666666667</v>
+        <v>2.969487179487179</v>
       </c>
     </row>
     <row r="17">
@@ -2267,13 +2330,13 @@
         <v>9</v>
       </c>
       <c r="E17" t="n">
-        <v>2.976666666666667</v>
+        <v>2.969487179487179</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Zilio Stefano</t>
+          <t>Giorgi Stefano</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2288,7 +2351,7 @@
         <v>9</v>
       </c>
       <c r="E18" t="n">
-        <v>2.976666666666667</v>
+        <v>2.969487179487179</v>
       </c>
     </row>
     <row r="19">
@@ -2309,7 +2372,7 @@
         <v>9</v>
       </c>
       <c r="E19" t="n">
-        <v>2.976666666666667</v>
+        <v>2.969487179487179</v>
       </c>
     </row>
     <row r="20">
@@ -2330,118 +2393,118 @@
         <v>9</v>
       </c>
       <c r="E20" t="n">
-        <v>2.976666666666667</v>
+        <v>2.969487179487179</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Muca Adrian</t>
+          <t>Zilio Stefano</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Professional Milano</t>
+          <t>Dirigente Milano</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2.958333333333333</v>
+        <v>3</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E21" t="n">
-        <v>2.897058823529412</v>
+        <v>2.969487179487179</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Fumagalli Alessandro</t>
+          <t>Moraja Marco</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Professional Milano</t>
+          <t>Dirigente Milano</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>2.958333333333333</v>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E22" t="n">
-        <v>2.897058823529412</v>
+        <v>2.969487179487179</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Cadoppi Andrea</t>
+          <t xml:space="preserve">Bianchi Liberato </t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Dirigente Milano</t>
+          <t>Professional Avezzano</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>2.958333333333333</v>
       </c>
       <c r="D23" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E23" t="n">
-        <v>2.976666666666667</v>
+        <v>2.866770833333333</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Moraja Marco</t>
+          <t>Fernicola Alessandra</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Dirigente Milano</t>
+          <t>Professional Milano</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>2.958333333333333</v>
       </c>
       <c r="D24" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E24" t="n">
-        <v>2.976666666666667</v>
+        <v>2.897058823529412</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bianchi Liberato </t>
+          <t>Cadoppi Andrea</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Professional Avezzano</t>
+          <t>Dirigente Milano</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>2.958333333333333</v>
       </c>
       <c r="D25" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E25" t="n">
-        <v>2.854166666666667</v>
+        <v>2.969487179487179</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Fernicola Alessandra</t>
+          <t>Fumagalli Alessandro</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2462,7 +2525,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Calderoni Gabriele Maria</t>
+          <t>Muca Adrian</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2471,10 +2534,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2.916666666666667</v>
+        <v>2.958333333333333</v>
       </c>
       <c r="D27" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E27" t="n">
         <v>2.897058823529412</v>
@@ -2483,43 +2546,43 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Valcamonica Marco</t>
+          <t>Calderoni Gabriele Maria</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Dirigente Milano</t>
+          <t>Professional Milano</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>2.916666666666667</v>
       </c>
       <c r="D28" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E28" t="n">
-        <v>2.976666666666667</v>
+        <v>2.897058823529412</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Foglia Emanuela</t>
+          <t>Francesconi Luigia</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Dirigente Milano</t>
+          <t>Dirigente Avezzano</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>2.916666666666667</v>
       </c>
       <c r="D29" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.976666666666667</v>
+        <v>2.875</v>
       </c>
     </row>
     <row r="30">
@@ -2540,76 +2603,76 @@
         <v>16</v>
       </c>
       <c r="E30" t="n">
-        <v>2.976666666666667</v>
+        <v>2.969487179487179</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Santella Gianni</t>
+          <t>Valcamonica Marco</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Dirigente Avezzano</t>
+          <t>Dirigente Milano</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>2.916666666666667</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E31" t="n">
-        <v>2.875</v>
+        <v>2.969487179487179</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Francesconi Luigia</t>
+          <t>Foglia Emanuela</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Dirigente Avezzano</t>
+          <t>Dirigente Milano</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>2.916666666666667</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E32" t="n">
-        <v>2.875</v>
+        <v>2.969487179487179</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Di Sabatino Bruno</t>
+          <t>Piccirilli Gianluca</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Dirigente Avezzano</t>
+          <t>Professional Avezzano</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>2.916666666666667</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E33" t="n">
-        <v>2.875</v>
+        <v>2.866770833333333</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Tartaglia Vincenzo</t>
+          <t>Santella Gianni</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2630,49 +2693,49 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Piccirilli Gianluca</t>
+          <t>Tartaglia Vincenzo</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Professional Avezzano</t>
+          <t>Dirigente Avezzano</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>2.916666666666667</v>
       </c>
       <c r="D35" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.854166666666667</v>
+        <v>2.875</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Castrigano Luca </t>
+          <t>Di Sabatino Bruno</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Professional Avezzano</t>
+          <t>Dirigente Avezzano</t>
         </is>
       </c>
       <c r="C36" t="n">
+        <v>2.916666666666667</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
         <v>2.875</v>
-      </c>
-      <c r="D36" t="n">
-        <v>6</v>
-      </c>
-      <c r="E36" t="n">
-        <v>2.854166666666667</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Margutti Pasquale</t>
+          <t xml:space="preserve">Castrigano Luca </t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2684,16 +2747,16 @@
         <v>2.875</v>
       </c>
       <c r="D37" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E37" t="n">
-        <v>2.854166666666667</v>
+        <v>2.866770833333333</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cercaci Alessandra</t>
+          <t>Macchi Giorgio</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2714,22 +2777,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Toia Luca Luigi</t>
+          <t>Margutti Pasquale</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Professional Milano</t>
+          <t>Professional Avezzano</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>2.875</v>
       </c>
       <c r="D39" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E39" t="n">
-        <v>2.897058823529412</v>
+        <v>2.866770833333333</v>
       </c>
     </row>
     <row r="40">
@@ -2756,7 +2819,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Macchi Giorgio</t>
+          <t>Cercaci Alessandra</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2777,70 +2840,70 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Alacqua Stefano</t>
+          <t>Toia Luca Luigi</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Dirigente Milano</t>
+          <t>Professional Milano</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2.833333333333333</v>
+        <v>2.875</v>
       </c>
       <c r="D42" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E42" t="n">
-        <v>2.976666666666667</v>
+        <v>2.897058823529412</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Ceriani Massimo</t>
+          <t>Lamura Sabrina</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Professional Milano</t>
+          <t>Professional Avezzano</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>2.833333333333333</v>
       </c>
       <c r="D43" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E43" t="n">
-        <v>2.897058823529412</v>
+        <v>2.866770833333333</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Lamura Sabrina</t>
+          <t>Zucchi Imerio</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Professional Avezzano</t>
+          <t>Dirigente Milano</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>2.833333333333333</v>
       </c>
       <c r="D44" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E44" t="n">
-        <v>2.854166666666667</v>
+        <v>2.969487179487179</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Zucchi Imerio</t>
+          <t>Gallina Paolo</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2855,34 +2918,34 @@
         <v>19</v>
       </c>
       <c r="E45" t="n">
-        <v>2.976666666666667</v>
+        <v>2.969487179487179</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Gallina Paolo</t>
+          <t>Ceriani Massimo</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Dirigente Milano</t>
+          <t>Professional Milano</t>
         </is>
       </c>
       <c r="C46" t="n">
         <v>2.833333333333333</v>
       </c>
       <c r="D46" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E46" t="n">
-        <v>2.976666666666667</v>
+        <v>2.897058823529412</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Nicolosi Dario</t>
+          <t>Alacqua Stefano</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2891,19 +2954,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2.791666666666667</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="D47" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E47" t="n">
-        <v>2.976666666666667</v>
+        <v>2.969487179487179</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Tradani Susanna</t>
+          <t>Maccalini Enrico</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2918,55 +2981,55 @@
         <v>22</v>
       </c>
       <c r="E48" t="n">
-        <v>2.976666666666667</v>
+        <v>2.969487179487179</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Properzi Massimiliano</t>
+          <t>Farina Simona</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Dirigente Avezzano</t>
+          <t>Professional Milano</t>
         </is>
       </c>
       <c r="C49" t="n">
         <v>2.791666666666667</v>
       </c>
       <c r="D49" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E49" t="n">
-        <v>2.875</v>
+        <v>2.897058823529412</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Diego Gi Giampietro </t>
+          <t>Nicolosi Dario</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Dirigente Avezzano</t>
+          <t>Dirigente Milano</t>
         </is>
       </c>
       <c r="C50" t="n">
         <v>2.791666666666667</v>
       </c>
       <c r="D50" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="E50" t="n">
-        <v>2.875</v>
+        <v>2.969487179487179</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Maccalini Enrico</t>
+          <t>Tradani Susanna</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2981,223 +3044,223 @@
         <v>22</v>
       </c>
       <c r="E51" t="n">
-        <v>2.976666666666667</v>
+        <v>2.969487179487179</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Farina Simona</t>
+          <t xml:space="preserve">Diego Gi Giampietro </t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Professional Milano</t>
+          <t>Dirigente Avezzano</t>
         </is>
       </c>
       <c r="C52" t="n">
         <v>2.791666666666667</v>
       </c>
       <c r="D52" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E52" t="n">
-        <v>2.897058823529412</v>
+        <v>2.875</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Volpa Alessandra </t>
+          <t>Properzi Massimiliano</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Professional Avezzano</t>
+          <t>Dirigente Avezzano</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2.75</v>
+        <v>2.791666666666667</v>
       </c>
       <c r="D53" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E53" t="n">
-        <v>2.854166666666667</v>
+        <v>2.875</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Premoli Gianluca</t>
+          <t>De cesaro Franco</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Professional Milano</t>
+          <t>Dirigente Milano</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="D54" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E54" t="n">
-        <v>2.897058823529412</v>
+        <v>2.969487179487179</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Campanello Marco</t>
+          <t>Alesii Genuino</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Professional Milano</t>
+          <t>Professional Avezzano</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="D55" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E55" t="n">
-        <v>2.897058823529412</v>
+        <v>2.866770833333333</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Roberto Rocca</t>
+          <t>Tellone Giuliano</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Professional Milano</t>
+          <t>Professional Avezzano</t>
         </is>
       </c>
       <c r="C56" t="n">
         <v>2.75</v>
       </c>
       <c r="D56" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E56" t="n">
-        <v>2.897058823529412</v>
+        <v>2.866770833333333</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">De Amicis Alvaro </t>
+          <t>Premoli Gianluca</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Professional Avezzano</t>
+          <t>Professional Milano</t>
         </is>
       </c>
       <c r="C57" t="n">
         <v>2.75</v>
       </c>
       <c r="D57" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E57" t="n">
-        <v>2.854166666666667</v>
+        <v>2.897058823529412</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Tellone Giuliano</t>
+          <t>Roberto Rocca</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Professional Avezzano</t>
+          <t>Professional Milano</t>
         </is>
       </c>
       <c r="C58" t="n">
         <v>2.75</v>
       </c>
       <c r="D58" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E58" t="n">
-        <v>2.854166666666667</v>
+        <v>2.897058823529412</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Di Paolo Massimo</t>
+          <t>Campanello Marco</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Professional Avezzano</t>
+          <t>Professional Milano</t>
         </is>
       </c>
       <c r="C59" t="n">
         <v>2.75</v>
       </c>
       <c r="D59" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E59" t="n">
-        <v>2.854166666666667</v>
+        <v>2.897058823529412</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Fumagalli Luca</t>
+          <t>Di Paolo Massimo</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Dirigente Milano</t>
+          <t>Professional Avezzano</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2.708333333333333</v>
+        <v>2.75</v>
       </c>
       <c r="D60" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="E60" t="n">
-        <v>2.976666666666667</v>
+        <v>2.866770833333333</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Valieri Andrea</t>
+          <t xml:space="preserve">Volpa Alessandra </t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Professional Milano</t>
+          <t>Professional Avezzano</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2.708333333333333</v>
+        <v>2.75</v>
       </c>
       <c r="D61" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E61" t="n">
-        <v>2.897058823529412</v>
+        <v>2.866770833333333</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Palma Luca</t>
+          <t xml:space="preserve">De Amicis Alvaro </t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3206,54 +3269,117 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2.666666666666667</v>
+        <v>2.75</v>
       </c>
       <c r="D62" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E62" t="n">
-        <v>2.854166666666667</v>
+        <v>2.866770833333333</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Amabrini Fabio</t>
+          <t>Fumagalli Luca</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Professional Avezzano</t>
+          <t>Dirigente Milano</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2.666666666666667</v>
+        <v>2.708333333333333</v>
       </c>
       <c r="D63" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E63" t="n">
-        <v>2.854166666666667</v>
+        <v>2.969487179487179</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>Valieri Andrea</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Professional Milano</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>2.708333333333333</v>
+      </c>
+      <c r="D64" t="n">
+        <v>16</v>
+      </c>
+      <c r="E64" t="n">
+        <v>2.897058823529412</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Amabrini Fabio</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Professional Avezzano</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="D65" t="n">
+        <v>15</v>
+      </c>
+      <c r="E65" t="n">
+        <v>2.866770833333333</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Palma Luca</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Professional Avezzano</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="D66" t="n">
+        <v>15</v>
+      </c>
+      <c r="E66" t="n">
+        <v>2.866770833333333</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
           <t>Mauri Luca</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>Professional Milano</t>
         </is>
       </c>
-      <c r="C64" t="n">
+      <c r="C67" t="n">
         <v>2.5</v>
       </c>
-      <c r="D64" t="n">
+      <c r="D67" t="n">
         <v>17</v>
       </c>
-      <c r="E64" t="n">
+      <c r="E67" t="n">
         <v>2.897058823529412</v>
       </c>
     </row>
